--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488004_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488004_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5979</v>
+        <v>8.359</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6704</v>
+        <v>8.038399999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0725</v>
+        <v>0.3206</v>
       </c>
       <c r="G2" t="n">
         <v>4.8201</v>
@@ -610,13 +610,13 @@
         <v>0.7929</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.696</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0696</v>
+        <v>0.2984</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6263</v>
+        <v>-0.2332</v>
       </c>
       <c r="V2" t="n">
         <v>2.6808</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.067</v>
+        <v>6.7116</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9806</v>
+        <v>6.5129</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0864</v>
+        <v>0.1987</v>
       </c>
       <c r="G3" t="n">
         <v>2.3628</v>
@@ -688,13 +688,13 @@
         <v>0.7929</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7804</v>
+        <v>-0.1358</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1745</v>
+        <v>-0.6422</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3941</v>
+        <v>0.5064</v>
       </c>
       <c r="V3" t="n">
         <v>3.6917</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4716</v>
+        <v>5.012</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9597</v>
+        <v>4.837</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5119</v>
+        <v>0.175</v>
       </c>
       <c r="G4" t="n">
         <v>2.2433</v>
@@ -766,13 +766,13 @@
         <v>0.7929</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3753</v>
+        <v>0.1651</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9984</v>
+        <v>-0.121</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6231</v>
+        <v>0.2861</v>
       </c>
       <c r="V4" t="n">
         <v>1.8107</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5234</v>
+        <v>3.1398</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5494</v>
+        <v>2.3062</v>
       </c>
       <c r="F5" t="n">
-        <v>0.974</v>
+        <v>0.8336</v>
       </c>
       <c r="G5" t="n">
         <v>2.6369</v>
@@ -844,13 +844,13 @@
         <v>0.7929</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0847</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8591</v>
+        <v>0.6159</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2256</v>
+        <v>0.0852</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5903</v>
+        <v>1.5174</v>
       </c>
       <c r="E6" t="n">
-        <v>1.975</v>
+        <v>1.5094</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3847</v>
+        <v>0.0081</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.454</v>
+        <v>2.2145</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.9966</v>
+        <v>1.8184</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5426</v>
+        <v>0.3961</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6576</v>
+        <v>3.1813</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7927</v>
+        <v>2.0045</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4503</v>
+        <v>1.1768</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1115</v>
+        <v>-0.9668</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.2038</v>
+        <v>-0.1861</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0923</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
         <v>0.7929</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2316</v>
+        <v>0.2257</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1014</v>
+        <v>-0.2229</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1301</v>
+        <v>0.4486</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0109</v>
+        <v>0.2666</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2071</v>
+        <v>0.5331</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1962</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5226</v>
+        <v>0.7992</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4864</v>
+        <v>1.3243</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0362</v>
+        <v>-0.5251</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2145</v>
+        <v>-0.454</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8184</v>
+        <v>-2.9966</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3961</v>
+        <v>2.5426</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1813</v>
+        <v>0.6576</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0045</v>
+        <v>-0.7927</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1768</v>
+        <v>1.4503</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9668</v>
+        <v>-1.1115</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1861</v>
+        <v>-2.2038</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7806999999999999</v>
+        <v>1.0923</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
         <v>0.7929</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2309</v>
+        <v>0.4405</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2458</v>
+        <v>0.4507</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4767</v>
+        <v>-0.0103</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2666</v>
+        <v>1.0109</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5331</v>
+        <v>1.2071</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2666</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9514</v>
+        <v>0.6001</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5853</v>
+        <v>1.1778</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6338</v>
+        <v>-0.5777</v>
       </c>
       <c r="G8" t="n">
         <v>0.4331</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5183</v>
+        <v>0.167</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6167</v>
+        <v>0.2093</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>J. AGÜERA ZEA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.3027</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.3027</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7793</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3744</v>
+        <v>0.3027</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5325</v>
+        <v>0.3027</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8419</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4639</v>
+        <v>0.3027</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5442</v>
+        <v>0.3027</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0804</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9105</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0118</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9223</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7216</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5581</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1635</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. AGÜERA ZEA</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3027</v>
+        <v>0.1063</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3027</v>
+        <v>-0.3922</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.4985</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3027</v>
+        <v>-1.3744</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3027</v>
+        <v>-0.5325</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0.8419</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3027</v>
+        <v>-0.4639</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3027</v>
+        <v>-0.5442</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.0804</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-0.9105</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.0118</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.9223</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.9544</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.0717</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.8827</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0736</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1436</v>
+        <v>0.1666</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.2385</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7971</v>
@@ -1390,13 +1390,13 @@
         <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5448</v>
+        <v>0.3992</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2458</v>
+        <v>-0.2229</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7905</v>
+        <v>0.6221</v>
       </c>
       <c r="V12" t="n">
         <v>0.5331</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6697</v>
+        <v>-0.2631</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4844</v>
+        <v>-2.2182</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8147</v>
+        <v>1.9551</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4483</v>
@@ -1468,13 +1468,13 @@
         <v>0.7929</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3029</v>
+        <v>0.7094</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2423</v>
+        <v>0.5085</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0605</v>
+        <v>0.2009</v>
       </c>
       <c r="V13" t="n">
         <v>0.674</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.3482</v>
+        <v>-2.1901</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.7143</v>
+        <v>-1.6125</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6338</v>
+        <v>-0.5777</v>
       </c>
       <c r="G14" t="n">
         <v>-0.998</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.359</v>
+        <v>-0.201</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.2103</v>
+        <v>-3.3411</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.4798</v>
+        <v>-2.9475</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7305</v>
+        <v>-0.3936</v>
       </c>
       <c r="G15" t="n">
         <v>-3.5562</v>
@@ -1624,13 +1624,13 @@
         <v>0.7929</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1298</v>
+        <v>-0.2606</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0497</v>
+        <v>-0.5174</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0801</v>
+        <v>0.2568</v>
       </c>
       <c r="V15" t="n">
         <v>0.674</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>20.0485</v>
+        <v>20.9846</v>
       </c>
       <c r="E16" t="n">
-        <v>18.3715</v>
+        <v>19.3076</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6772</v>
+        <v>1.677</v>
       </c>
       <c r="G16" t="n">
         <v>5.6881</v>
@@ -1672,7 +1672,7 @@
         <v>-2.3475</v>
       </c>
       <c r="I16" t="n">
-        <v>8.0358</v>
+        <v>8.035799999999998</v>
       </c>
       <c r="J16" t="n">
         <v>16.1281</v>
@@ -1681,7 +1681,7 @@
         <v>9.621799999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>6.506300000000001</v>
+        <v>6.506299999999998</v>
       </c>
       <c r="M16" t="n">
         <v>-10.4399</v>
@@ -1699,16 +1699,16 @@
         <v>-6.9377</v>
       </c>
       <c r="R16" t="n">
-        <v>7.929000000000001</v>
+        <v>7.929000000000002</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2943</v>
+        <v>3.2302</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5309999999999999</v>
+        <v>0.4052</v>
       </c>
       <c r="U16" t="n">
-        <v>2.8251</v>
+        <v>2.825</v>
       </c>
       <c r="V16" t="n">
         <v>11.0752</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.9547</v>
+        <v>2.5978</v>
       </c>
       <c r="E17" t="n">
-        <v>4.8925</v>
+        <v>3.5681</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9377</v>
+        <v>-0.9704</v>
       </c>
       <c r="G17" t="n">
         <v>2.3393</v>
@@ -1780,13 +1780,13 @@
         <v>0.3964</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7672</v>
+        <v>0.4102</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7292</v>
+        <v>0.4049</v>
       </c>
       <c r="U17" t="n">
-        <v>0.038</v>
+        <v>0.0053</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5482</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3459</v>
+        <v>2.0194</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2857</v>
+        <v>3.1838</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9398</v>
+        <v>-1.1644</v>
       </c>
       <c r="G18" t="n">
         <v>0.7189</v>
@@ -1858,13 +1858,13 @@
         <v>1.1893</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5587</v>
+        <v>0.2322</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2972</v>
+        <v>-0.399</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8558</v>
+        <v>0.6312</v>
       </c>
       <c r="V18" t="n">
         <v>0.8701</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.435</v>
+        <v>0.6623</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6007</v>
+        <v>0.8044</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1657</v>
+        <v>-0.1422</v>
       </c>
       <c r="G19" t="n">
         <v>0.0137</v>
@@ -1936,13 +1936,13 @@
         <v>0.7929</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.442</v>
+        <v>-0.2148</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8625</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4205</v>
+        <v>0.444</v>
       </c>
       <c r="V19" t="n">
         <v>0.0704</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1063</v>
+        <v>0.0237</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0555</v>
+        <v>0.0464</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0508</v>
+        <v>-0.0227</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2608</v>
@@ -2014,13 +2014,13 @@
         <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0437</v>
+        <v>0.0863</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.154</v>
+        <v>-1.4276</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5918</v>
+        <v>0.7955</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7458</v>
+        <v>-2.2231</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6974</v>
@@ -2092,13 +2092,13 @@
         <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1128</v>
+        <v>-0.3864</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6826</v>
+        <v>-0.4788</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5698</v>
+        <v>0.0925</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1367</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>A. PEREZ GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7671</v>
+        <v>-1.5312</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.419</v>
+        <v>-0.2324</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3481</v>
+        <v>-1.2988</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1698</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5620000000000001</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3922</v>
+        <v>-0.4899</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8179</v>
+        <v>0.1878</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4931</v>
+        <v>0.0271</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6752</v>
+        <v>0.1607</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6481</v>
+        <v>-1.1782</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9312</v>
+        <v>-0.5276</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2831</v>
+        <v>-0.6506</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1982</v>
+        <v>0.1982</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.265</v>
+        <v>-0.8094</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2458</v>
+        <v>-0.4202</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0192</v>
+        <v>-0.3892</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4737</v>
+        <v>0.0704</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4737</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. PEREZ GARCIA</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9831</v>
+        <v>-1.6443</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4362</v>
+        <v>-0.5209</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5469</v>
+        <v>-1.1234</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9903999999999999</v>
+        <v>0.1698</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5004999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4899</v>
+        <v>-0.3922</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1878</v>
+        <v>0.8179</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0271</v>
+        <v>1.4931</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1607</v>
+        <v>-0.6752</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1782</v>
+        <v>-0.6481</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5276</v>
+        <v>-0.9312</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6506</v>
+        <v>0.2831</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1982</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2613</v>
+        <v>-0.1422</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.624</v>
+        <v>-0.3477</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6373</v>
+        <v>0.2055</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0704</v>
+        <v>-1.4737</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0704</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5024</v>
+        <v>-2.8759</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0937</v>
+        <v>-1.603</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4087</v>
+        <v>-1.2728</v>
       </c>
       <c r="G24" t="n">
         <v>0.3419</v>
@@ -2326,13 +2326,13 @@
         <v>0.3964</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0514</v>
+        <v>-0.4249</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1837</v>
+        <v>-0.3256</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2351</v>
+        <v>-0.0993</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2071</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2441</v>
+        <v>-4.5486</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1239</v>
+        <v>-1.5127</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1202</v>
+        <v>-3.0359</v>
       </c>
       <c r="G25" t="n">
         <v>-3.0842</v>
@@ -2404,13 +2404,13 @@
         <v>0.5947</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3403</v>
+        <v>0.3552</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5616</v>
+        <v>0.0496</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2213</v>
+        <v>0.3055</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4142</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.4391</v>
+        <v>-5.2249</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.1611</v>
+        <v>-2.0592</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.278</v>
+        <v>-3.1657</v>
       </c>
       <c r="G26" t="n">
         <v>-3.0603</v>
@@ -2482,13 +2482,13 @@
         <v>0.3964</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8942</v>
+        <v>-0.68</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2899</v>
+        <v>-0.1881</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.4919</v>
       </c>
       <c r="V26" t="n">
         <v>-1.8811</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-8.5883</v>
+        <v>-7.4201</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.7584</v>
+        <v>-4.1472</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.8299</v>
+        <v>-3.2729</v>
       </c>
       <c r="G27" t="n">
         <v>-1.1785</v>
@@ -2560,13 +2560,13 @@
         <v>1.1893</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.2095</v>
+        <v>-0.0413</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.1121</v>
+        <v>-0.5009</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.0974</v>
+        <v>0.4596</v>
       </c>
       <c r="V27" t="n">
         <v>-3.4252</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-20.0488</v>
+        <v>-19.3694</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.6771</v>
+        <v>-1.6772</v>
       </c>
       <c r="F28" t="n">
-        <v>-18.3716</v>
+        <v>-17.6923</v>
       </c>
       <c r="G28" t="n">
         <v>-5.687999999999999</v>
@@ -2638,13 +2638,13 @@
         <v>6.937600000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.2943</v>
+        <v>-1.6151</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.8252</v>
+        <v>-2.8251</v>
       </c>
       <c r="U28" t="n">
-        <v>0.5308000000000002</v>
+        <v>1.21</v>
       </c>
       <c r="V28" t="n">
         <v>-11.0753</v>
@@ -2653,7 +2653,7 @@
         <v>-1.363</v>
       </c>
       <c r="X28" t="n">
-        <v>-9.712200000000003</v>
+        <v>-9.712199999999999</v>
       </c>
     </row>
   </sheetData>
